--- a/2026sambong6/public/ox/ox-quiz-template.xlsx
+++ b/2026sambong6/public/ox/ox-quiz-template.xlsx
@@ -514,7 +514,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>5. 파일을 올리면 문제 은행이 이 파일 내용으로 바뀝니다. 최고 기록은 유지됩니다.</v>
+        <v>5. 올리기 기본은 추가입니다. 전체 바꾸기는 확인 후에만 문제 은행을 이 파일로 바꿉니다. 최고 기록은 유지됩니다.</v>
       </c>
     </row>
     <row r="8">
